--- a/assets/modelo_de_madurez/Ponderaciones por KPI.xlsx
+++ b/assets/modelo_de_madurez/Ponderaciones por KPI.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\!!!TRABAJO\UNIVERSIDAD\Doctorado\2023 - Semestre 1\Propuesta de tesis\MODELO DE MADUREZ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\!!!! TESIS\RoadmapGenerator\assets\modelo_de_madurez\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B9FD15A-0D4E-4FF2-8D04-00C90AF5F3A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4089F556-0047-45ED-89DB-4DB5F91814E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Pequeñas empresas" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="43">
   <si>
     <t>KPI</t>
   </si>
@@ -38,9 +38,6 @@
   </si>
   <si>
     <t>KDA</t>
-  </si>
-  <si>
-    <t>Inventarios y Sostenibilidad Hídrica</t>
   </si>
   <si>
     <t>Manejo del riego</t>
@@ -193,9 +190,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -482,20 +477,20 @@
   <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="54.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="44.42578125" customWidth="1"/>
     <col min="2" max="2" width="20.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="43.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>0</v>
       </c>
       <c r="D1" t="s">
@@ -503,296 +498,296 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="2">
+      <c r="C5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="1" t="s">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D8" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" s="1" t="s">
+      <c r="B10" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" s="1" t="s">
+      <c r="C10" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="D10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C11" s="1" t="s">
+      <c r="D11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>21</v>
       </c>
-      <c r="D11" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
+      <c r="B12" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="C12" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="D12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" t="s">
         <v>24</v>
       </c>
-      <c r="D12" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C13" s="1" t="s">
+      <c r="D13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" t="s">
         <v>25</v>
       </c>
-      <c r="D13" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B14" s="1" t="s">
+      <c r="C14" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="D14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" t="s">
         <v>27</v>
       </c>
-      <c r="D14" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C15" s="1" t="s">
+      <c r="D15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B16" t="s">
         <v>28</v>
       </c>
-      <c r="D15" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B16" s="1" t="s">
+      <c r="C16" t="s">
         <v>29</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="D16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>21</v>
+      </c>
+      <c r="B17" t="s">
+        <v>28</v>
+      </c>
+      <c r="C17" t="s">
         <v>30</v>
       </c>
-      <c r="D16" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C17" s="1" t="s">
+      <c r="D17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>31</v>
       </c>
-      <c r="D17" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
+      <c r="B18" t="s">
         <v>32</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="C18" t="s">
         <v>33</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="D18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>31</v>
+      </c>
+      <c r="B19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C19" t="s">
         <v>34</v>
       </c>
-      <c r="D18" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C19" s="1" t="s">
+      <c r="D19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>31</v>
+      </c>
+      <c r="B20" t="s">
         <v>35</v>
       </c>
-      <c r="D19" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B20" s="1" t="s">
+      <c r="C20" t="s">
         <v>36</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="D20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>31</v>
+      </c>
+      <c r="B21" t="s">
         <v>37</v>
       </c>
-      <c r="D20" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B21" s="1" t="s">
+      <c r="C21" t="s">
         <v>38</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="D21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>31</v>
+      </c>
+      <c r="B22" t="s">
+        <v>37</v>
+      </c>
+      <c r="C22" t="s">
         <v>39</v>
       </c>
-      <c r="D21" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D22" s="2">
+      <c r="D22">
         <v>2</v>
       </c>
     </row>
@@ -803,332 +798,331 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9A96797-507A-4E69-8A89-32C2E7A24859}">
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="54.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="54.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="43.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="2" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" t="s">
         <v>0</v>
       </c>
       <c r="D1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B2" s="2" t="s">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" t="s">
         <v>6</v>
       </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="F2" s="2"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" t="s">
         <v>7</v>
       </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" t="s">
         <v>8</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>9</v>
       </c>
       <c r="D4">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" t="s">
         <v>11</v>
       </c>
-      <c r="D5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>12</v>
       </c>
-      <c r="D6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
+      <c r="B7" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" t="s">
         <v>15</v>
       </c>
-      <c r="D7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" t="s">
         <v>16</v>
       </c>
-      <c r="D8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" s="2" t="s">
+      <c r="C9" t="s">
         <v>17</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>18</v>
       </c>
       <c r="D9">
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" s="2" t="s">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" t="s">
         <v>20</v>
       </c>
-      <c r="D10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C11" s="2" t="s">
+      <c r="D11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>21</v>
       </c>
-      <c r="D11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
+      <c r="B12" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="C12" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="D12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" t="s">
         <v>24</v>
       </c>
-      <c r="D12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C13" s="2" t="s">
+      <c r="D13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" t="s">
         <v>25</v>
       </c>
-      <c r="D13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B14" s="2" t="s">
+      <c r="C14" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="D14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" t="s">
         <v>27</v>
       </c>
-      <c r="D14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C15" s="2" t="s">
+      <c r="D15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B16" t="s">
         <v>28</v>
       </c>
-      <c r="D15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B16" s="2" t="s">
+      <c r="C16" t="s">
         <v>29</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="D16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>21</v>
+      </c>
+      <c r="B17" t="s">
+        <v>28</v>
+      </c>
+      <c r="C17" t="s">
         <v>30</v>
       </c>
-      <c r="D16">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C17" s="2" t="s">
+      <c r="D17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>31</v>
       </c>
-      <c r="D17">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
+      <c r="B18" t="s">
         <v>32</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="C18" t="s">
         <v>33</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="D18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>31</v>
+      </c>
+      <c r="B19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C19" t="s">
         <v>34</v>
       </c>
-      <c r="D18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C19" s="2" t="s">
+      <c r="D19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>31</v>
+      </c>
+      <c r="B20" t="s">
         <v>35</v>
       </c>
-      <c r="D19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B20" s="2" t="s">
+      <c r="C20" t="s">
+        <v>42</v>
+      </c>
+      <c r="D20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>31</v>
+      </c>
+      <c r="B21" t="s">
+        <v>35</v>
+      </c>
+      <c r="C21" t="s">
         <v>36</v>
       </c>
-      <c r="C20" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D20">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C21" s="2" t="s">
+      <c r="D21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>31</v>
+      </c>
+      <c r="B22" t="s">
         <v>37</v>
       </c>
-      <c r="D21">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B22" s="2" t="s">
+      <c r="C22" t="s">
         <v>38</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="D22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>31</v>
+      </c>
+      <c r="B23" t="s">
+        <v>37</v>
+      </c>
+      <c r="C23" t="s">
         <v>39</v>
-      </c>
-      <c r="D22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>40</v>
       </c>
       <c r="D23">
         <v>2</v>
